--- a/astro-site/public/dl/haccp-templates/11-corrective-action-log.xlsx
+++ b/astro-site/public/dl/haccp-templates/11-corrective-action-log.xlsx
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="L5" s="25" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="M5" s="20" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Incident type" error="Pick a type from the list." type="list" errorStyle="stop">
-      <formula1>"Temperature,Rejected product,Cleaning,Pests,Customer complaint,Allergen,Contamination,Expired / date mark,Traceability,Training,Other"</formula1>
+      <formula1>"Temperature,Rejected product,Cleaning,Pests,Customer complaint,Allergen,Contamination,Expiry / date mark,Traceability,Training,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Source log" error="Pick the log where the deviation was detected. That is what lets you reconstruct the case: without it, the incident is left hanging and cannot be verified." type="list" errorStyle="stop">
       <formula1>"01 Food temperatures,02 Receiving temps,04 Daily cleaning,05 Receiving checklist,06 Traceability,07 Pest control,08 Allergens,09 Fryer oil,10 Water,16 Cooking &amp; reheating,17 Cooling &amp; thawing,18 Parasite destruction,19 Thermometers,Other"</formula1>
